--- a/INSTANCES/instances_xlsx/A_MTN_8/273FL_10A_3.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_8/273FL_10A_3.xlsx
@@ -9011,7 +9011,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -9028,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
